--- a/artfynd/A 17915-2024 artfynd.xlsx
+++ b/artfynd/A 17915-2024 artfynd.xlsx
@@ -948,7 +948,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117942691</v>
+        <v>117942770</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -983,19 +983,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1004,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513348</v>
+        <v>513448</v>
       </c>
       <c r="R4" t="n">
-        <v>6732228</v>
+        <v>6732178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1039,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,12 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En del hade blomstänglar med knoppar.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,14 +1067,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117942770</v>
+        <v>117942691</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1122,11 +1109,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1135,10 +1130,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513448</v>
+        <v>513348</v>
       </c>
       <c r="R5" t="n">
-        <v>6732178</v>
+        <v>6732228</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1170,7 +1165,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,7 +1175,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En del hade blomstänglar med knoppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17915-2024 artfynd.xlsx
+++ b/artfynd/A 17915-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117942770</v>
+        <v>117942691</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -983,11 +983,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -996,10 +1004,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513448</v>
+        <v>513348</v>
       </c>
       <c r="R4" t="n">
-        <v>6732178</v>
+        <v>6732228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1049,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En del hade blomstänglar med knoppar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,17 +1080,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117942691</v>
+        <v>117942770</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,19 +1122,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1130,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513348</v>
+        <v>513448</v>
       </c>
       <c r="R5" t="n">
-        <v>6732228</v>
+        <v>6732178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1165,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,12 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En del hade blomstänglar med knoppar.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17915-2024 artfynd.xlsx
+++ b/artfynd/A 17915-2024 artfynd.xlsx
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117942691</v>
+        <v>118792228</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,43 +960,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1004,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513348</v>
+        <v>513403</v>
       </c>
       <c r="R4" t="n">
-        <v>6732228</v>
+        <v>6732276</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,24 +1029,14 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En del hade blomstänglar med knoppar.</t>
+          <t>Tall med hack vid roten,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,14 +1045,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1080,7 +1056,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1213,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118792228</v>
+        <v>117942691</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,35 +1201,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1261,13 +1245,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513403</v>
+        <v>513348</v>
       </c>
       <c r="R6" t="n">
-        <v>6732276</v>
+        <v>6732228</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1294,14 +1278,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tall med hack vid roten,</t>
+          <t>En del hade blomstänglar med knoppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,8 +1304,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog som gränsar till myr. Blandbarrskog med stort lövinslag/mycket död ved, olika sphagnummossor. Mycket mygg!!!!</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
